--- a/CodeDo_Editor_capacity_with_visual_explanations.xlsx
+++ b/CodeDo_Editor_capacity_with_visual_explanations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/PersonalProjects/CodeDo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/PersonalProjects/CodeDoRN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D3ABE5-CD62-FB40-B737-355C6D37B426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE95A5F-1F81-344D-90AF-E3EBBB2EE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="801">
   <si>
     <t>World</t>
   </si>
@@ -41,9 +41,15 @@
     <t>Visual Explanation</t>
   </si>
   <si>
+    <t>Verified editor capability (audited 2026-10-14, Worlds 1-16)</t>
+  </si>
+  <si>
     <t>1. Kotlin Awakening</t>
   </si>
   <si>
+    <t>WORLD 1 SUMMARY: 54 of 54 Learn/Explore programs run or reproduce their intended error; 0 disabled; 13 of 13 lessons fully runnable. Quiz bank: 147 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>What is Kotlin?</t>
   </si>
   <si>
@@ -59,15 +65,48 @@
     <t>Not needed — text and code examples are sufficient</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 0 of 0 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: no Write &amp; Run stage in this lesson.
+Debug: no Debug stage in this lesson.</t>
+  </si>
+  <si>
     <t>Kotlin Syntax &amp; main()</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.</t>
+  </si>
+  <si>
     <t>print() and println()</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 match real kotlinc (1 documented limit).</t>
+  </si>
+  <si>
     <t>val vs var</t>
   </si>
   <si>
@@ -83,63 +122,181 @@
     <t>Int &amp; Long</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Long is a JS number: exact only up to 2^53; Long.MAX_VALUE is reported as unsupported.
+Topic audit: numbers 98/99 match real kotlinc (1 documented limit).</t>
+  </si>
+  <si>
     <t>Float &amp; Double</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 match real kotlinc (1 documented limit).</t>
+  </si>
+  <si>
     <t>Boolean</t>
   </si>
   <si>
     <t>Char</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Known limits: 'a'.compareTo('c') and 'a'.plus(2) cannot be told from String versions (use 'a' + 2).
+Topic audit: chars 32/34 match real kotlinc (2 documented limits).</t>
+  </si>
+  <si>
     <t>Strings</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: strings 109/109 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>String Templates</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: strings 109/109 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Personal Profile Program</t>
   </si>
   <si>
     <t>2. Operator Forge</t>
   </si>
   <si>
+    <t>WORLD 2 SUMMARY: 47 of 47 Learn/Explore programs run or reproduce their intended error; 0 disabled; 7 of 7 lessons fully runnable. Quiz bank: 90 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Arithmetic operators</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Comparison operators</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Logical operators</t>
   </si>
   <si>
     <t>Assignment operators</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 8 of 8 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Int ++, -- and += do not wrap at 32 bits (only + - * in expressions do).
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Increment / decrement</t>
   </si>
   <si>
     <t>Animated execution trace — prefix vs postfix value changes</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Int ++, -- and += do not wrap at 32 bits (only + - * in expressions do).
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Operator precedence</t>
   </si>
   <si>
     <t>Animated evaluation tree — show operation order step by step</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Smart Calculator</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: numbers 98/99 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>3. Decision Maker</t>
   </si>
   <si>
+    <t>WORLD 3 SUMMARY: 52 of 52 Learn/Explore programs run or reproduce their intended error; 0 disabled; 9 of 9 lessons fully runnable. Quiz bank: 94 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>if</t>
   </si>
   <si>
     <t>Decision flowchart — condition branches to execute or skip</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: decisions 28/28 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>if-else</t>
   </si>
   <si>
@@ -152,6 +309,15 @@
     <t>Animated branching flowchart — conditions checked in order</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: decisions 28/28 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>when</t>
   </si>
   <si>
@@ -179,36 +345,93 @@
     <t>Type checks with is where appropriate</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: decisions 28/28 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Grade &amp; Eligibility System</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: decisions 28/28 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>4. Loop Master</t>
   </si>
   <si>
+    <t>WORLD 4 SUMMARY: 69 of 69 Learn/Explore programs run or reproduce their intended error; 0 disabled; 11 of 11 lessons fully runnable. Quiz bank: 128 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>for</t>
   </si>
   <si>
     <t>Animated loop trace — iterator, current item, body, repeat</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: ranges 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>while</t>
   </si>
   <si>
     <t>Animated loop flowchart — check before each iteration</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: ranges 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>do-while</t>
   </si>
   <si>
     <t>Animated loop flowchart — execute once, then check</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: ranges 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Ranges</t>
   </si>
   <si>
     <t>Static number-line visual — inclusive bounds and membership</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: ranges 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Progressions</t>
   </si>
   <si>
@@ -248,12 +471,33 @@
     <t>Pattern &amp; Number Analyzer</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: ranges 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>5. Function Forge</t>
   </si>
   <si>
+    <t>WORLD 5 SUMMARY: 44 of 44 Learn/Explore programs run or reproduce their intended error; 0 disabled; 9 of 9 lessons fully runnable. Quiz bank: 104 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Defining functions</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: functions 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Function parameters</t>
   </si>
   <si>
@@ -287,6 +531,15 @@
     <t>Static scope diagram — local function visible only inside parent</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: functions 57/57 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>vararg</t>
   </si>
   <si>
@@ -299,36 +552,84 @@
     <t>6. Collection Valley</t>
   </si>
   <si>
+    <t>WORLD 6 SUMMARY: 48 of 48 Learn/Explore programs run or reproduce their intended error; 0 disabled; 11 of 11 lessons fully runnable. Quiz bank: 128 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Arrays</t>
   </si>
   <si>
     <t>Indexed-slot diagram — fixed positions and element access</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: arrays 45/45 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Lists</t>
   </si>
   <si>
     <t>Indexed sequence diagram — ordered elements and access</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Sets</t>
   </si>
   <si>
     <t>Static uniqueness diagram — duplicate values collapse</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: sets 35/35 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Maps</t>
   </si>
   <si>
     <t>Key–value lookup diagram</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: maps 71/71 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Mutable vs read-only collections</t>
   </si>
   <si>
     <t>Side-by-side state diagram — allowed and blocked changes</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: collection topics: arrays 45/45, lists 139/139, sets 35/35, maps 71/71 match real kotlinc.</t>
+  </si>
+  <si>
     <t>Creating and accessing collections</t>
   </si>
   <si>
@@ -341,6 +642,15 @@
     <t>Animated before/after collection state</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: collection topics: arrays 45/45, lists 139/139, sets 35/35, maps 71/71 match real kotlinc.</t>
+  </si>
+  <si>
     <t>Iterating over collections</t>
   </si>
   <si>
@@ -350,24 +660,54 @@
     <t>Basic collection operations</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: collection topics: arrays 45/45, lists 139/139, sets 35/35, maps 71/71 match real kotlinc.</t>
+  </si>
+  <si>
     <t>Choosing the right collection type</t>
   </si>
   <si>
     <t>Decision flowchart — order, uniqueness and key lookup</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: no Write &amp; Run stage in this lesson.
+Debug: no Debug stage in this lesson.
+Topic audit: collection topics: arrays 45/45, lists 139/139, sets 35/35, maps 71/71 match real kotlinc.</t>
+  </si>
+  <si>
     <t>Student Records</t>
   </si>
   <si>
     <t>7. Null Safety Shield</t>
   </si>
   <si>
+    <t>WORLD 7 SUMMARY: 68 of 68 Learn/Explore programs run or reproduce their intended error; 0 disabled; 11 of 11 lessons fully runnable. Quiz bank: 132 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Nullable types</t>
   </si>
   <si>
     <t>Static type-state diagram — value or null</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: nulls 46/46 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Nullable variables</t>
   </si>
   <si>
@@ -380,18 +720,45 @@
     <t>Animated null-propagation trace — continue or return null</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: nulls 46/46 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Elvis operator ?:</t>
   </si>
   <si>
     <t>Decision flowchart — nullable value or fallback</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: nulls 46/46 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Non-null assertion !!</t>
   </si>
   <si>
     <t>Risk flowchart — value continues or throws on null</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 4 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: nulls 46/46 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Null checks</t>
   </si>
   <si>
@@ -404,6 +771,15 @@
     <t>Type-refinement diagram — check narrows the usable type</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: nulls 46/46 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Safe casts as?</t>
   </si>
   <si>
@@ -428,12 +804,24 @@
     <t>8. Object Kingdom</t>
   </si>
   <si>
+    <t>WORLD 8 SUMMARY: 55 of 56 Learn/Explore programs run or reproduce their intended error; 1 disabled; 13 of 14 lessons fully runnable. Quiz bank: 158 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Classes</t>
   </si>
   <si>
     <t>Class blueprint diagram — properties and methods</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Objects</t>
   </si>
   <si>
@@ -470,6 +858,15 @@
     <t>Access-boundary diagram — public, internal, protected and private</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: no Write &amp; Run stage in this lesson.
+Debug: no Debug stage in this lesson.
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Data classes</t>
   </si>
   <si>
@@ -503,9 +900,22 @@
     <t>Student Grade Manager</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 4 programs disabled)
+Learn example: NOT runnable in the editor (Try it disabled).
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 3 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Learn example "Grading a single student" - smart cast of a nullable property
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>9. Lambda Lab</t>
   </si>
   <si>
+    <t>WORLD 9 SUMMARY: 66 of 66 Learn/Explore programs run or reproduce their intended error; 0 disabled; 12 of 12 lessons fully runnable. Quiz bank: 138 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Lambda expressions</t>
   </si>
   <si>
@@ -515,12 +925,30 @@
     <t>Animated data-flow diagram — input → lambda body → result</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Anonymous functions</t>
   </si>
   <si>
     <t>Expression and block bodies, typed-context parameter inference, receiver functions and local early returns are verified.</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Function types</t>
   </si>
   <si>
@@ -530,6 +958,15 @@
     <t>Function-signature diagram — parameter types → return type</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Higher-order functions</t>
   </si>
   <si>
@@ -539,12 +976,30 @@
     <t>Function-flow diagram — function passed in, invoked and/or returned</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>it</t>
   </si>
   <si>
     <t>Implicit single parameters and nested shadowing work. A zero-argument lambda can retain the outer it.</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Function references</t>
   </si>
   <si>
@@ -572,6 +1027,15 @@
     <t>Labelled control-flow diagram — exit lambda without exiting caller</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Inline functions</t>
   </si>
   <si>
@@ -584,6 +1048,16 @@
     <t>Conceptual expansion diagram — call site before vs inlined body</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 3 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>noinline</t>
   </si>
   <si>
@@ -593,6 +1067,16 @@
     <t>Callback-routing diagram — selected lambda remains a function object</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>crossinline</t>
   </si>
   <si>
@@ -611,9 +1095,22 @@
     <t>Extendable</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lambdas 60/60 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>10. Collection Wizardry</t>
   </si>
   <si>
+    <t>WORLD 10 SUMMARY: 56 of 56 Learn/Explore programs run or reproduce their intended error; 0 disabled; 10 of 10 lessons fully runnable. Quiz bank: 114 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>map &amp; mapNotNull &amp; filter</t>
   </si>
   <si>
@@ -623,6 +1120,15 @@
     <t>Animated collection pipeline — transform, remove nulls and filter</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>filterNot &amp; filterIsInstance &amp; flatMap</t>
   </si>
   <si>
@@ -632,6 +1138,16 @@
     <t>Animated collection pipeline — exclude, type-select and flatten</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>flatten &amp; reduce &amp; fold</t>
   </si>
   <si>
@@ -641,6 +1157,15 @@
     <t>Animated aggregation trace — nested items flatten and accumulator evolves</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>groupBy &amp; associate &amp; partition</t>
   </si>
   <si>
@@ -659,6 +1184,15 @@
     <t>Animated grouping diagram — pair, chunk and sliding window</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>distinct &amp; sorted</t>
   </si>
   <si>
@@ -668,6 +1202,16 @@
     <t>Animated transformation — deduplicate then reorder</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>sortedBy &amp; min / max</t>
   </si>
   <si>
@@ -692,6 +1236,15 @@
     <t>Animated pipeline with short-circuit — stop at first match</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 4 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: lists 139/139, maps 71/71 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Data Transformation Engine</t>
   </si>
   <si>
@@ -701,6 +1254,9 @@
     <t>11. OOP Evolution</t>
   </si>
   <si>
+    <t>WORLD 11 SUMMARY: 98 of 106 Learn/Explore programs run or reproduce their intended error; 8 disabled; 6 of 14 lessons fully runnable. Quiz bank: 163 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Inheritance &amp; Abstract classes</t>
   </si>
   <si>
@@ -710,6 +1266,16 @@
     <t>Class hierarchy diagram — abstract contract and concrete subclasses</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 9 programs disabled)
+Learn example: runs and matches.
+Explore: 7 of 8 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 8 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 07 "final override" - Unexpected token 'function'
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Interfaces &amp; Multiple interface implementation</t>
   </si>
   <si>
@@ -719,6 +1285,16 @@
     <t>Relationship diagram — one class satisfies multiple contracts</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 8 programs disabled)
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 02 "Abstract + default member" - Invalid or unexpected token
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Sealed classes &amp; Sealed interfaces</t>
   </si>
   <si>
@@ -728,12 +1304,32 @@
     <t>Closed hierarchy diagram — permitted variants and exhaustive handling</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: classes/OOP 90/90 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Data classes in domain modeling &amp; Enum classes</t>
   </si>
   <si>
     <t>Already built in World 8</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 9 programs disabled)
+Learn example: runs and matches.
+Explore: 7 of 8 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 8 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 02 "Hash code agreement" - a.hashCode is not a function
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Nested classes</t>
   </si>
   <si>
@@ -743,6 +1339,16 @@
     <t>Containment diagram — nested type without outer-instance link</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: classes/OOP 90/90 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Inner classes</t>
   </si>
   <si>
@@ -752,9 +1358,29 @@
     <t>Object-link diagram — inner instance retains outer reference</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 6 programs disabled)
+Learn example: runs and matches.
+Explore: 4 of 5 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 05 "Compile boundary" - Unexpected token 'class'
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Object declarations</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 05 "Object expression" - Unexpected token ':'
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Companion objects</t>
   </si>
   <si>
@@ -764,6 +1390,16 @@
     <t>Ownership diagram — class-level companion vs instance members</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: classes/OOP 90/90 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Extension functions</t>
   </si>
   <si>
@@ -800,6 +1436,16 @@
     <t>Property-access flow — get/set routed through delegate</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 8 programs disabled)
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 04 "Custom mutable delegate" - Unexpected identifier 'by'
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Visibility and API design</t>
   </si>
   <si>
@@ -809,15 +1455,38 @@
     <t>Same limitation as World 8's Visibility Modifiers -- no runtime enforcement to verify</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 06 "Compile boundary external private set" - engine cannot reproduce this compile error
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Domain Model Engine</t>
   </si>
   <si>
     <t>Depends on several not-yet-built features above</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 9 programs disabled)
+Learn example: runs and matches.
+Explore: 7 of 8 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 8 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 03 "Derived extension" - cents is not defined
+Topic audit: classes/OOP 90/90 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>12. Generic Realm</t>
   </si>
   <si>
+    <t>WORLD 12 SUMMARY: 95 of 108 Learn/Explore programs run or reproduce their intended error; 13 disabled; 5 of 15 lessons fully runnable. Quiz bank: 169 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Generic classes</t>
   </si>
   <si>
@@ -827,6 +1496,17 @@
     <t>Reusable type-template diagram — T replaced by concrete types</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 01 "Explicit type argument" - Type mismatch: expected Box&lt;Int&gt;, got Boolean
+Known limit: A whole Double stored in a generic class type parameter prints without ".0".
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Generic functions</t>
   </si>
   <si>
@@ -836,6 +1516,16 @@
     <t>Type-substitution diagram — call infers T from arguments</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (2 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 4 of 6 cards run and print the stored output; 2 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 02 "Explicit argument" - Int is not defined | Explore card 06 "Two type parameters model different roles" - Unexpected identifier 'pair'
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Type parameters</t>
   </si>
   <si>
@@ -845,6 +1535,16 @@
     <t>Not Runnable</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Generic constraints</t>
   </si>
   <si>
@@ -854,6 +1554,16 @@
     <t>Type-bound diagram — accepted and rejected type arguments</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Multiple constraints</t>
   </si>
   <si>
@@ -869,12 +1579,32 @@
     <t>Variance direction diagram — consumer accepts supertypes</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 03 "Illegal output" - engine cannot reproduce this compile error
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>out variance</t>
   </si>
   <si>
     <t>Variance direction diagram — producer returns subtypes safely</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 7 programs disabled)
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 03 "Illegal input" - engine cannot reproduce this compile error
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Invariance</t>
   </si>
   <si>
@@ -887,18 +1617,48 @@
     <t>Type-hierarchy arrows — variance declared on the generic type</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Use-site variance</t>
   </si>
   <si>
     <t>Projection diagram — variance applied at one usage site</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 8 programs disabled)
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 05 "in projection supports consuming values" - Type mismatch: expected MutableList, got Int
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Star projections</t>
   </si>
   <si>
     <t>Unknown-type access diagram — safe operations with *</t>
   </si>
   <si>
+    <t>VERDICT: PARTLY RUNNABLE (3 of 7 programs disabled)
+Learn example: NOT runnable in the editor (Try it disabled).
+Explore: 4 of 6 cards run and print the stored output; 2 have Try it disabled (listed below).
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Learn example "Work Safely with an Unknown Type Argument" - star projection `List&lt;*&gt;` | Explore card 05 "Star projection is not Any type argument" - Unexpected identifier 'unknown' | Explore card 06 "Mutable star projection blocks arbitrary writes" - Unexpected identifier 'xs'
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Reified type parameters</t>
   </si>
   <si>
@@ -908,27 +1668,70 @@
     <t>Runtime type-availability diagram — erased T vs reified T</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 8 programs disabled)
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 01 "Ordinary erasure" - engine cannot reproduce this compile error
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Type aliases</t>
   </si>
   <si>
     <t>An alternate name only; trivial no-op substitution</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 6 programs disabled)
+Learn example: NOT runnable in the editor (Try it disabled).
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Learn example "Give an Existing Type a Clearer Name" - typealias with generics
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Type-safe generic APIs</t>
   </si>
   <si>
     <t>Runs as ordinary code once types are stripped</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 8 programs disabled)
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 05 "Tie input and output with the same T" - Wrong argument count for firstOrNull: expected 1
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>Generic Data Toolkit</t>
   </si>
   <si>
     <t>Runs fine as ordinary generic-looking code</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 9 programs disabled)
+Learn example: runs and matches.
+Explore: 7 of 8 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 8 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 08 "Reified helper handles runtime type selection" - filterIsInstance supports String, Boolean, Number and declared classes; primitive numeric 
+Topic audit: No topic-coverage cases written yet (generics): evidence is the lesson run results above plus the quiz checks.</t>
+  </si>
+  <si>
     <t>13. Scope Masters</t>
   </si>
   <si>
+    <t>WORLD 13 SUMMARY: 69 of 69 Learn/Explore programs run or reproduce their intended error; 0 disabled; 10 of 10 lessons fully runnable. Quiz bank: 112 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>let &amp; run</t>
   </si>
   <si>
@@ -938,6 +1741,16 @@
     <t>Receiver/return-value comparison diagram — it vs this and lambda result</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: builders 24/25 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>apply</t>
   </si>
   <si>
@@ -947,6 +1760,16 @@
     <t>Receiver/return diagram — this receiver, original object returned</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: builders 24/25 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>also</t>
   </si>
   <si>
@@ -986,6 +1809,16 @@
     <t>Decision flowchart — receiver style and desired return value</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: builders 24/25 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Scope-function chaining</t>
   </si>
   <si>
@@ -1001,12 +1834,36 @@
     <t>Best-practice guidance, not a testable behavior</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: builders 24/25 cases match real kotlinc.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Configuration Builder</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Indexing a StringBuilder with [] is not translated (use get or toString()[i]).
+Topic audit: builders 24/25 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>14. Sequence Dimension</t>
   </si>
   <si>
+    <t>WORLD 14 SUMMARY: 90 of 90 Learn/Explore programs run or reproduce their intended error; 0 disabled; 13 of 13 lessons fully runnable. Quiz bank: 149 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>What sequences are</t>
   </si>
   <si>
@@ -1016,6 +1873,16 @@
     <t>Eager-vs-lazy conceptual pipeline</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (sequences): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Eager collection processing</t>
   </si>
   <si>
@@ -1040,6 +1907,16 @@
     <t>generator-based sequence factory, buildable</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (sequences): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>asSequence()</t>
   </si>
   <si>
@@ -1064,6 +1941,16 @@
     <t>Trigger animation — terminal call starts sequence evaluation</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (sequences): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Sequence evaluation order</t>
   </si>
   <si>
@@ -1097,18 +1984,41 @@
     <t>Real JVM performance isn't measurable in-browser JS; only ordering/evaluation-count claims are honest</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (sequences): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>When sequences should and should not be used</t>
   </si>
   <si>
     <t>Mostly reasoning guidance, though backed by real runnable examples</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: No topic-coverage cases written yet (sequences): evidence is the lesson run results above plus the quiz checks.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Large Dataset Processor</t>
   </si>
   <si>
     <t>15. Error Fortress</t>
   </si>
   <si>
+    <t>WORLD 15 SUMMARY: 103 of 104 Learn/Explore programs run or reproduce their intended error; 1 disabled; 14 of 15 lessons fully runnable. Quiz bank: 170 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Exceptions &amp; try</t>
   </si>
   <si>
@@ -1118,6 +2028,16 @@
     <t>Exception control-flow diagram — normal path vs thrown path</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>catch</t>
   </si>
   <si>
@@ -1127,6 +2047,17 @@
     <t>Exception-routing flowchart — matching handler receives failure</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 3 of 5 cards run and print the stored output; 2 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: JDK message of an out-of-bounds read on a 1-element immutable list differs from kotlinc.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>finally</t>
   </si>
   <si>
@@ -1139,6 +2070,16 @@
     <t>Stack-unwinding animation — exception leaves current path</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 6 programs disabled)
+Learn example: NOT runnable in the editor (Try it disabled).
+Explore: 3 of 5 cards run and print the stored output; 2 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Learn example "Signal an Invalid State with throw" - `else throw` on the next line
+Topic audit: exceptions 41/42 cases match real kotlinc.</t>
+  </si>
+  <si>
     <t>Multiple catch blocks</t>
   </si>
   <si>
@@ -1148,6 +2089,16 @@
     <t>Exception-type routing flowchart</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>try as an expression</t>
   </si>
   <si>
@@ -1157,18 +2108,48 @@
     <t>Branch-result diagram — try/catch produces a value</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Custom exceptions</t>
   </si>
   <si>
     <t>class MyError : Exception(...) maps to extending JS Error</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 5 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Checked vs unchecked exception model</t>
   </si>
   <si>
     <t>Kotlin itself has no checked exceptions -- mostly a comparative/conceptual note</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: reproduces its intended error.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: no Write &amp; Run stage in this lesson.
+Debug: no Debug stage in this lesson.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Result</t>
   </si>
   <si>
@@ -1178,6 +2159,16 @@
     <t>Success/failure state container diagram</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>runCatching</t>
   </si>
   <si>
@@ -1196,18 +2187,58 @@
     <t>Two-track pipeline — success and failure operations</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 8 of 8 cards run and print the stored output.
+Predict: 8 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Partial / simulated" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Error-handling patterns</t>
   </si>
   <si>
     <t>Ordinary try/catch composition, already runnable</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Runnable" / "Extendable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Avoiding swallowed errors</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 6 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: no Write &amp; Run stage in this lesson.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Designing meaningful failure paths</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 7 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Topic audit: exceptions 41/42 cases match real kotlinc.
+Note: older columns C/E say "Conceptual only" / "Not Runnable" for this lesson; the measured result above is higher.</t>
+  </si>
+  <si>
     <t>Reliable Order Engine</t>
   </si>
   <si>
@@ -1217,6 +2248,9 @@
     <t>16. Coroutine Academy</t>
   </si>
   <si>
+    <t>WORLD 16 SUMMARY: 72 of 73 Learn/Explore programs run or reproduce their intended error; 1 disabled; 11 of 12 lessons fully runnable. Quiz bank: 139 questions (executable answers checked against real kotlinc).</t>
+  </si>
+  <si>
     <t>Coroutine fundamentals &amp; Coroutine builders</t>
   </si>
   <si>
@@ -1226,6 +2260,16 @@
     <t>Animated coroutine timeline — start, suspend, resume and complete</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 4 of 4 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>launch &amp; async</t>
   </si>
   <si>
@@ -1235,6 +2279,16 @@
     <t>Side-by-side lifecycle timeline — Job vs Deferred result</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>await &amp; Suspending functions</t>
   </si>
   <si>
@@ -1244,6 +2298,16 @@
     <t>Animated suspension timeline — caller pauses without blocking thread</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 6 of 6 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>suspend &amp; Coroutine context</t>
   </si>
   <si>
@@ -1262,6 +2326,17 @@
     <t>Relationship diagram — coroutine, Job lifecycle and dispatcher selection</t>
   </si>
   <si>
+    <t>VERDICT: RUNNABLE WITH GAPS (1 of 6 programs disabled)
+Learn example: runs and matches.
+Explore: 4 of 5 cards run and print the stored output; 1 have Try it disabled (listed below).
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+NOT RUNNABLE (Try it disabled): Explore card 05 "Main availability" - Suspend function 'label' can be called only from a coroutine or another suspend function
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>Cancellation &amp; Cooperative cancellation</t>
   </si>
   <si>
@@ -1271,6 +2346,16 @@
     <t>Job-state animation — cancel request reaches suspension/check point</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 5 of 5 cards run and print the stored output.
+Predict: 6 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>Structured concurrency</t>
   </si>
   <si>
@@ -1307,6 +2392,16 @@
     <t>Failure-propagation flowchart — launch/async and parent/child paths</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: reproduces its intended error.
+Explore: 4 of 5 cards run and print the stored output; 1 more intentionally show a compile/runtime error and the editor reproduces it.
+Predict: 5 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>Coroutine best practices</t>
   </si>
   <si>
@@ -1322,6 +2417,16 @@
     <t>Built and execution-verified: the full boss integration (owned Deferred combination, dispatcher-aware async, launch+join side effects, deterministic result assembly, ordinary vs. supervised failure policy, withContext result flow) is runnable and verified end-to-end against every Learn/Explore/Predict/Write&amp;Run/Debug snippet plus the full regression suite, zero regressions.</t>
   </si>
   <si>
+    <t>VERDICT: FULLY RUNNABLE
+Learn example: runs and matches.
+Explore: 7 of 7 cards run and print the stored output.
+Predict: 7 questions (reading-only stage; answers are not executed by this check).
+Write &amp; Run: solution reproduces the expected output; the unfinished starter fails as designed.
+Debug: fixed code passes; the broken version fails as designed.
+Known limit: Real threads and wall-clock timing are not supported (Tier 3); coroutines use simulated scheduling.
+Topic audit: No topic-coverage cases (coroutines run on a simulated scheduler, not real threads): evidence is the lesson run results above, test:world16-coroutines and the World 16 quiz programs checked against real kotlinc.</t>
+  </si>
+  <si>
     <t>17. Flow Universe</t>
   </si>
   <si>
@@ -2018,10 +3123,16 @@
     <t>Meaning</t>
   </si>
   <si>
+    <t>New column H (Curriculum sheet)</t>
+  </si>
+  <si>
     <t>Implemented and execution-verified for the scope stated in Note. This does not certify complete lesson content or all Kotlin compiler behavior.</t>
   </si>
   <si>
     <t>Already runnable in the editor/engine.</t>
+  </si>
+  <si>
+    <t>Measured on 2026-10-14 by running every Learn example, Explore card, Write &amp; Run solution/starter and Debug fix of Worlds 1-16 through the editor engine. Columns C and E are older estimates and were not changed.</t>
   </si>
   <si>
     <t>Not yet built, but maps cleanly to real JS with high fidelity -- same scope of effort as Worlds 1-8.</t>
@@ -2043,7 +3154,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2078,6 +3189,30 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2133,7 +3268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2168,6 +3303,19 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2402,18 +3550,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G344"/>
+  <dimension ref="A1:H344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="8" max="8" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2432,3426 +3582,4035 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="12"/>
       <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E4" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="E5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E6" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E10" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E11" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E13" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E14" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E15" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="12"/>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="12"/>
       <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E19" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E20" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E21" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G21" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E22" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E25" s="12"/>
       <c r="G25" s="16"/>
     </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="12"/>
       <c r="G26" s="16"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H26" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G34" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E35" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E36" s="12"/>
       <c r="G36" s="16"/>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="12"/>
       <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H37" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E49" s="12"/>
       <c r="G49" s="16"/>
     </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="12"/>
       <c r="G50" s="16"/>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H50" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G51" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E52" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="H54" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="H55" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G56" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E57" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+      <c r="H57" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E60" s="12"/>
       <c r="G60" s="16"/>
     </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="12"/>
       <c r="G61" s="16"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H61" s="18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="H66" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+      <c r="H69" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G70" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E71" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+      <c r="H71" s="19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H72" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E73" s="12"/>
       <c r="G73" s="16"/>
     </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="12"/>
       <c r="G74" s="16"/>
-    </row>
-    <row r="75" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H74" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="H77" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="H78" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+      <c r="H79" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+      <c r="H80" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+      <c r="H81" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+      <c r="H82" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+      <c r="H83" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H85" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E86" s="12"/>
       <c r="G86" s="16"/>
     </row>
-    <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="12"/>
       <c r="G87" s="16"/>
-    </row>
-    <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H87" s="18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+      <c r="H88" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+      <c r="H89" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G90" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" t="s">
-        <v>140</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E91" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G91" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" t="s">
-        <v>141</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E92" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+      <c r="H92" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G93" s="16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+      <c r="H93" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+      <c r="H94" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+      <c r="H95" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="H96" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+      <c r="H97" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="H98" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+      <c r="H99" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="H100" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H101" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E102" s="12"/>
       <c r="G102" s="16"/>
     </row>
-    <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="12"/>
       <c r="G103" s="16"/>
-    </row>
-    <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H103" s="18" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+      <c r="H104" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H105" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>222</v>
+      </c>
+      <c r="H106" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+      <c r="H107" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H108" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+      <c r="H109" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+      <c r="H110" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+      <c r="H111" s="19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>183</v>
+        <v>241</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="H112" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+      <c r="H113" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+      <c r="H114" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H115" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E116" s="12"/>
       <c r="G116" s="16"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="12"/>
       <c r="G117" s="16"/>
-    </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H117" s="18" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="H118" s="19" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>200</v>
+        <v>263</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+      <c r="H119" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+      <c r="H120" s="19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+      <c r="H121" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="H122" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="H123" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+      <c r="H124" s="19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H125" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+      <c r="H126" s="19" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H127" s="19" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="12"/>
       <c r="G128" s="16"/>
     </row>
-    <row r="129" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="12"/>
       <c r="G129" s="16"/>
-    </row>
-    <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H129" s="18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+      <c r="H130" s="19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+      <c r="H131" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G132" s="16" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="H132" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>235</v>
+        <v>307</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G133" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H133" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>238</v>
+        <v>311</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+      <c r="H134" s="19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
-        <v>240</v>
+        <v>314</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G135" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="H135" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>318</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" s="19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>320</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" t="s">
-        <v>243</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E136" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G136" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" t="s">
-        <v>244</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>184</v>
-      </c>
       <c r="D137" s="4" t="s">
-        <v>245</v>
+        <v>321</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+      <c r="H137" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>248</v>
+        <v>325</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+      <c r="H138" s="19" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" t="s">
-        <v>250</v>
+        <v>327</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>251</v>
+        <v>328</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+      <c r="H139" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>254</v>
+        <v>331</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G140" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="H140" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>333</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E141" s="12" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" t="s">
-        <v>256</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E141" s="12" t="s">
-        <v>195</v>
-      </c>
       <c r="G141" s="16" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+      <c r="H141" s="19" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>261</v>
+        <v>339</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H142" s="19" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G143" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H143" s="19" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="12"/>
       <c r="G144" s="16"/>
     </row>
-    <row r="145" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>264</v>
+        <v>344</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="12"/>
       <c r="G145" s="16"/>
-    </row>
-    <row r="146" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H145" s="18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>265</v>
+        <v>346</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G146" s="16" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+      <c r="H146" s="19" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G147" s="16" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="H147" s="19" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
-        <v>271</v>
+        <v>354</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>272</v>
+        <v>355</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G148" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H148" s="19" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G149" s="16" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="H149" s="19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
-        <v>277</v>
+        <v>362</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G150" s="16" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+      <c r="H150" s="19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
-        <v>279</v>
+        <v>364</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+      <c r="H151" s="19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G152" s="16" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+      <c r="H152" s="19" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
-        <v>284</v>
+        <v>371</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G153" s="16" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+      <c r="H153" s="19" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B154" t="s">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G154" s="16" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+      <c r="H154" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G155" s="16" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+      <c r="H155" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B156" t="s">
-        <v>290</v>
+        <v>379</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>280</v>
+        <v>365</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G156" s="16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+      <c r="H156" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B157" t="s">
-        <v>292</v>
+        <v>382</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>293</v>
+        <v>383</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G157" s="16" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+      <c r="H157" s="19" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" t="s">
-        <v>295</v>
+        <v>386</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>296</v>
+        <v>387</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G158" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H158" s="19" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B159" t="s">
-        <v>297</v>
+        <v>389</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G159" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H159" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B160" t="s">
-        <v>299</v>
+        <v>392</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>300</v>
+        <v>393</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G160" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H160" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="12"/>
       <c r="G161" s="16"/>
     </row>
-    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>301</v>
+        <v>395</v>
       </c>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="12"/>
       <c r="G162" s="16"/>
-    </row>
-    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H162" s="18" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163" t="s">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>303</v>
+        <v>398</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G163" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+      <c r="H163" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B164" t="s">
-        <v>305</v>
+        <v>401</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+      <c r="H164" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B165" t="s">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G165" s="16" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+      <c r="H165" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B166" t="s">
-        <v>310</v>
+        <v>407</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G166" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="H166" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B167" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G167" s="16" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+      <c r="H167" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B168" t="s">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G168" s="16" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+      <c r="H168" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B169" t="s">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>319</v>
+        <v>416</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G169" s="16" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+      <c r="H169" s="19" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
-        <v>321</v>
+        <v>419</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>322</v>
+        <v>420</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G170" s="16" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+      <c r="H170" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>324</v>
+        <v>422</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G171" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H171" s="19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>326</v>
+        <v>425</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G172" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H172" s="19" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="12"/>
       <c r="G173" s="16"/>
     </row>
-    <row r="174" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="12"/>
       <c r="G174" s="16"/>
-    </row>
-    <row r="175" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H174" s="18" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B175" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>329</v>
+        <v>430</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G175" s="16" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+      <c r="H175" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B176" t="s">
-        <v>331</v>
+        <v>433</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>332</v>
+        <v>434</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G176" s="16" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+      <c r="H176" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B177" t="s">
-        <v>334</v>
+        <v>436</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G177" s="16" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+      <c r="H177" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B178" t="s">
-        <v>337</v>
+        <v>439</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>338</v>
+        <v>440</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G178" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H178" s="19" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B179" t="s">
-        <v>339</v>
+        <v>442</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>340</v>
+        <v>443</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G179" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H179" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B180" t="s">
-        <v>341</v>
+        <v>444</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>342</v>
+        <v>445</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G180" s="16" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+      <c r="H180" s="19" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>344</v>
+        <v>447</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>345</v>
+        <v>448</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G181" s="16" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+      <c r="H181" s="19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>347</v>
+        <v>451</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>348</v>
+        <v>452</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G182" s="16" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+      <c r="H182" s="19" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>351</v>
+        <v>455</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G183" s="16" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+      <c r="H183" s="19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B184" t="s">
-        <v>353</v>
+        <v>457</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G184" s="16" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+      <c r="H184" s="19" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B185" t="s">
-        <v>356</v>
+        <v>460</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>357</v>
+        <v>461</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G185" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H185" s="19" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B186" t="s">
-        <v>358</v>
+        <v>463</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>359</v>
+        <v>464</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G186" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H186" s="19" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B187" t="s">
-        <v>360</v>
+        <v>466</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G187" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H187" s="19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="12"/>
       <c r="G188" s="16"/>
     </row>
-    <row r="189" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>361</v>
+        <v>467</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="12"/>
       <c r="G189" s="16"/>
-    </row>
-    <row r="190" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H189" s="18" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" t="s">
-        <v>362</v>
+        <v>469</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>363</v>
+        <v>470</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G190" s="16" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+      <c r="H190" s="19" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B191" t="s">
-        <v>365</v>
+        <v>473</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="E191" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G191" s="16" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="H191" s="19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B192" t="s">
-        <v>368</v>
+        <v>477</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="E192" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G192" s="16" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+      <c r="H192" s="19" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B193" t="s">
-        <v>370</v>
+        <v>479</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="E193" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G193" s="16" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+      <c r="H193" s="19" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B194" t="s">
-        <v>372</v>
+        <v>482</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>373</v>
+        <v>483</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G194" s="16" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+      <c r="H194" s="19" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B195" t="s">
-        <v>375</v>
+        <v>486</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>376</v>
+        <v>487</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G195" s="16" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+      <c r="H195" s="19" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
-        <v>378</v>
+        <v>490</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>379</v>
+        <v>491</v>
       </c>
       <c r="E196" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G196" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H196" s="19" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B197" t="s">
-        <v>380</v>
+        <v>493</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>381</v>
+        <v>494</v>
       </c>
       <c r="E197" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G197" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H197" s="19" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B198" t="s">
-        <v>382</v>
+        <v>496</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>383</v>
+        <v>497</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G198" s="16" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+      <c r="H198" s="19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B199" t="s">
-        <v>385</v>
+        <v>500</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>386</v>
+        <v>501</v>
       </c>
       <c r="E199" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G199" s="16" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+      <c r="H199" s="19" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B200" t="s">
-        <v>388</v>
+        <v>503</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>389</v>
+        <v>504</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G200" s="16" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+      <c r="H200" s="19" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B201" t="s">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>392</v>
+        <v>508</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G201" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H201" s="19" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B202" t="s">
-        <v>393</v>
+        <v>510</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G202" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H202" s="19" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B203" t="s">
-        <v>394</v>
+        <v>512</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G203" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H203" s="19" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" t="s">
-        <v>395</v>
+        <v>514</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>396</v>
+        <v>515</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G204" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H204" s="19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E205" s="12"/>
       <c r="G205" s="16"/>
     </row>
-    <row r="206" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>397</v>
+        <v>516</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="12"/>
       <c r="G206" s="16"/>
-    </row>
-    <row r="207" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H206" s="18" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B207" s="13" t="s">
-        <v>398</v>
+        <v>518</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>399</v>
+        <v>519</v>
       </c>
       <c r="E207" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F207">
         <v>1</v>
       </c>
       <c r="G207" s="16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+      <c r="H207" s="19" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B208" t="s">
-        <v>401</v>
+        <v>522</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>402</v>
+        <v>523</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F208">
         <v>2</v>
       </c>
       <c r="G208" s="16" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+      <c r="H208" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B209" t="s">
-        <v>404</v>
+        <v>526</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>405</v>
+        <v>527</v>
       </c>
       <c r="E209" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F209">
         <v>3</v>
       </c>
       <c r="G209" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+      <c r="H209" s="19" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B210" t="s">
-        <v>407</v>
+        <v>530</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>408</v>
+        <v>531</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F210">
         <v>4</v>
       </c>
       <c r="G210" s="16" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+      <c r="H210" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="179.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B211" t="s">
-        <v>410</v>
+        <v>533</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>411</v>
+        <v>534</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G211" s="16" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>535</v>
+      </c>
+      <c r="H211" s="19" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B212" t="s">
-        <v>413</v>
+        <v>537</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>414</v>
+        <v>538</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F212">
         <v>6</v>
       </c>
       <c r="G212" s="16" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>539</v>
+      </c>
+      <c r="H212" s="19" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B213" t="s">
-        <v>416</v>
+        <v>541</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>417</v>
+        <v>542</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F213">
         <v>7</v>
       </c>
       <c r="G213" s="16" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+      <c r="H213" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B214" t="s">
-        <v>419</v>
+        <v>544</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>420</v>
+        <v>545</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F214">
         <v>8</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>546</v>
+      </c>
+      <c r="H214" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B215" t="s">
-        <v>422</v>
+        <v>547</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>423</v>
+        <v>548</v>
       </c>
       <c r="E215" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F215">
         <v>9</v>
       </c>
       <c r="G215" s="16" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+      <c r="H215" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="166" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" t="s">
-        <v>425</v>
+        <v>550</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>426</v>
+        <v>551</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F216">
         <v>10</v>
       </c>
       <c r="G216" s="16" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+      <c r="H216" s="19" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B217" t="s">
-        <v>428</v>
+        <v>554</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>429</v>
+        <v>555</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G217" s="16" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>556</v>
+      </c>
+      <c r="H217" s="19" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="152.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B218" t="s">
-        <v>431</v>
+        <v>557</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>432</v>
+        <v>558</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F218">
         <v>12</v>
       </c>
       <c r="G218" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H218" s="19" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E219" s="12"/>
       <c r="G219" s="16"/>
     </row>
-    <row r="220" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>433</v>
+        <v>560</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -5859,174 +7618,174 @@
       <c r="E220" s="12"/>
       <c r="G220" s="16"/>
     </row>
-    <row r="221" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B221" t="s">
-        <v>434</v>
+        <v>561</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>435</v>
+        <v>562</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G221" s="16" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B222" t="s">
-        <v>437</v>
+        <v>564</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>438</v>
+        <v>565</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G222" s="16" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B223" t="s">
-        <v>440</v>
+        <v>567</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>441</v>
+        <v>568</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G223" s="16" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B224" t="s">
-        <v>443</v>
+        <v>570</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>444</v>
+        <v>571</v>
       </c>
       <c r="E224" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G224" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B225" t="s">
-        <v>445</v>
+        <v>572</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>446</v>
+        <v>573</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G225" s="16" t="s">
-        <v>447</v>
+        <v>574</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B226" t="s">
-        <v>448</v>
+        <v>575</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>449</v>
+        <v>576</v>
       </c>
       <c r="E226" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G226" s="16" t="s">
-        <v>450</v>
+        <v>577</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B227" t="s">
-        <v>451</v>
+        <v>578</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>452</v>
+        <v>579</v>
       </c>
       <c r="E227" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G227" s="16" t="s">
-        <v>453</v>
+        <v>580</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B228" t="s">
-        <v>454</v>
+        <v>581</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>455</v>
+        <v>582</v>
       </c>
       <c r="E228" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G228" s="16" t="s">
-        <v>456</v>
+        <v>583</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B229" t="s">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>458</v>
+        <v>585</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G229" s="16" t="s">
-        <v>459</v>
+        <v>586</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" t="s">
-        <v>460</v>
+        <v>587</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>461</v>
+        <v>588</v>
       </c>
       <c r="E230" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G230" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6035,7 +7794,7 @@
     </row>
     <row r="232" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>462</v>
+        <v>589</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -6045,240 +7804,240 @@
     </row>
     <row r="233" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B233" t="s">
-        <v>463</v>
+        <v>590</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>464</v>
+        <v>591</v>
       </c>
       <c r="E233" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G233" s="16" t="s">
-        <v>465</v>
+        <v>592</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B234" t="s">
-        <v>466</v>
+        <v>593</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>467</v>
+        <v>594</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G234" s="16" t="s">
-        <v>468</v>
+        <v>595</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B235" t="s">
-        <v>469</v>
+        <v>596</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>470</v>
+        <v>597</v>
       </c>
       <c r="E235" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G235" s="16" t="s">
-        <v>471</v>
+        <v>598</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B236" t="s">
-        <v>472</v>
+        <v>599</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>473</v>
+        <v>600</v>
       </c>
       <c r="E236" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G236" s="16" t="s">
-        <v>474</v>
+        <v>601</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B237" t="s">
-        <v>475</v>
+        <v>602</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>476</v>
+        <v>603</v>
       </c>
       <c r="E237" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G237" s="16" t="s">
-        <v>477</v>
+        <v>604</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B238" t="s">
-        <v>478</v>
+        <v>605</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>479</v>
+        <v>606</v>
       </c>
       <c r="E238" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G238" s="16" t="s">
-        <v>480</v>
+        <v>607</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B239" t="s">
-        <v>481</v>
+        <v>608</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>482</v>
+        <v>609</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G239" s="16" t="s">
-        <v>483</v>
+        <v>610</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B240" t="s">
-        <v>484</v>
+        <v>611</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>485</v>
+        <v>612</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G240" s="16" t="s">
-        <v>486</v>
+        <v>613</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B241" t="s">
-        <v>487</v>
+        <v>614</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>488</v>
+        <v>615</v>
       </c>
       <c r="E241" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G241" s="16" t="s">
-        <v>489</v>
+        <v>616</v>
       </c>
     </row>
     <row r="242" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B242" t="s">
-        <v>490</v>
+        <v>617</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>491</v>
+        <v>618</v>
       </c>
       <c r="E242" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G242" s="16" t="s">
-        <v>492</v>
+        <v>619</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B243" t="s">
-        <v>493</v>
+        <v>620</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>494</v>
+        <v>621</v>
       </c>
       <c r="E243" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G243" s="16" t="s">
-        <v>495</v>
+        <v>622</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B244" t="s">
-        <v>496</v>
+        <v>623</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E244" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G244" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B245" t="s">
-        <v>497</v>
+        <v>624</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E245" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G245" s="16" t="s">
-        <v>498</v>
+        <v>625</v>
       </c>
     </row>
     <row r="246" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B246" t="s">
-        <v>499</v>
+        <v>626</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>500</v>
+        <v>627</v>
       </c>
       <c r="E246" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G246" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6287,7 +8046,7 @@
     </row>
     <row r="248" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>501</v>
+        <v>628</v>
       </c>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -6297,274 +8056,274 @@
     </row>
     <row r="249" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B249" t="s">
-        <v>502</v>
+        <v>629</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>503</v>
+        <v>630</v>
       </c>
       <c r="E249" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G249" s="16" t="s">
-        <v>504</v>
+        <v>631</v>
       </c>
     </row>
     <row r="250" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B250" t="s">
-        <v>505</v>
+        <v>632</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>506</v>
+        <v>633</v>
       </c>
       <c r="E250" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G250" s="16" t="s">
-        <v>507</v>
+        <v>634</v>
       </c>
     </row>
     <row r="251" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B251" t="s">
-        <v>508</v>
+        <v>635</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>509</v>
+        <v>636</v>
       </c>
       <c r="E251" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G251" s="16" t="s">
-        <v>510</v>
+        <v>637</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B252" t="s">
-        <v>511</v>
+        <v>638</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>512</v>
+        <v>639</v>
       </c>
       <c r="E252" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G252" s="16" t="s">
-        <v>513</v>
+        <v>640</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B253" t="s">
-        <v>514</v>
+        <v>641</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>515</v>
+        <v>642</v>
       </c>
       <c r="E253" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G253" s="16" t="s">
-        <v>516</v>
+        <v>643</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B254" t="s">
-        <v>517</v>
+        <v>644</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>518</v>
+        <v>645</v>
       </c>
       <c r="E254" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G254" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B255" t="s">
-        <v>519</v>
+        <v>646</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>520</v>
+        <v>647</v>
       </c>
       <c r="E255" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G255" s="16" t="s">
-        <v>521</v>
+        <v>648</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B256" t="s">
-        <v>522</v>
+        <v>649</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>523</v>
+        <v>650</v>
       </c>
       <c r="E256" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G256" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="257" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B257" t="s">
-        <v>524</v>
+        <v>651</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>525</v>
+        <v>652</v>
       </c>
       <c r="E257" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G257" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B258" t="s">
-        <v>526</v>
+        <v>653</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>527</v>
+        <v>654</v>
       </c>
       <c r="E258" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G258" s="16" t="s">
-        <v>528</v>
+        <v>655</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B259" t="s">
-        <v>529</v>
+        <v>656</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>530</v>
+        <v>657</v>
       </c>
       <c r="E259" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G259" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B260" t="s">
-        <v>531</v>
+        <v>658</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>532</v>
+        <v>659</v>
       </c>
       <c r="E260" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G260" s="16" t="s">
-        <v>533</v>
+        <v>660</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B261" t="s">
-        <v>534</v>
+        <v>661</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>535</v>
+        <v>662</v>
       </c>
       <c r="E261" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G261" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B262" t="s">
-        <v>536</v>
+        <v>663</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>537</v>
+        <v>664</v>
       </c>
       <c r="E262" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G262" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B263" t="s">
-        <v>538</v>
+        <v>665</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>539</v>
+        <v>666</v>
       </c>
       <c r="E263" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G263" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B264" t="s">
-        <v>540</v>
+        <v>667</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>541</v>
+        <v>668</v>
       </c>
       <c r="E264" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G264" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6573,7 +8332,7 @@
     </row>
     <row r="266" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>542</v>
+        <v>669</v>
       </c>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -6583,172 +8342,172 @@
     </row>
     <row r="267" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B267" t="s">
-        <v>543</v>
+        <v>670</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>544</v>
+        <v>671</v>
       </c>
       <c r="E267" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G267" s="16" t="s">
-        <v>545</v>
+        <v>672</v>
       </c>
     </row>
     <row r="268" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B268" t="s">
-        <v>546</v>
+        <v>673</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>547</v>
+        <v>674</v>
       </c>
       <c r="E268" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G268" s="16" t="s">
-        <v>548</v>
+        <v>675</v>
       </c>
     </row>
     <row r="269" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B269" t="s">
-        <v>549</v>
+        <v>676</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>550</v>
+        <v>677</v>
       </c>
       <c r="E269" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G269" s="16" t="s">
-        <v>551</v>
+        <v>678</v>
       </c>
     </row>
     <row r="270" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B270" t="s">
-        <v>552</v>
+        <v>679</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>553</v>
+        <v>680</v>
       </c>
       <c r="E270" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G270" s="16" t="s">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B271" t="s">
-        <v>555</v>
+        <v>682</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>556</v>
+        <v>683</v>
       </c>
       <c r="E271" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G271" s="16" t="s">
-        <v>557</v>
+        <v>684</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B272" t="s">
-        <v>558</v>
+        <v>685</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>559</v>
+        <v>686</v>
       </c>
       <c r="E272" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G272" s="16" t="s">
-        <v>560</v>
+        <v>687</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B273" t="s">
-        <v>561</v>
+        <v>688</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>562</v>
+        <v>689</v>
       </c>
       <c r="E273" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G273" s="16" t="s">
-        <v>563</v>
+        <v>690</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B274" t="s">
-        <v>564</v>
+        <v>691</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>565</v>
+        <v>692</v>
       </c>
       <c r="E274" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G274" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B275" t="s">
-        <v>566</v>
+        <v>693</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>567</v>
+        <v>694</v>
       </c>
       <c r="E275" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G275" s="16" t="s">
-        <v>568</v>
+        <v>695</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B276" t="s">
-        <v>569</v>
+        <v>696</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>570</v>
+        <v>697</v>
       </c>
       <c r="E276" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G276" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6757,7 +8516,7 @@
     </row>
     <row r="278" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>571</v>
+        <v>698</v>
       </c>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -6767,257 +8526,257 @@
     </row>
     <row r="279" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B279" t="s">
-        <v>572</v>
+        <v>699</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>573</v>
+        <v>700</v>
       </c>
       <c r="E279" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G279" s="16" t="s">
-        <v>574</v>
+        <v>701</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B280" t="s">
-        <v>575</v>
+        <v>702</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>576</v>
+        <v>703</v>
       </c>
       <c r="E280" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G280" s="16" t="s">
-        <v>577</v>
+        <v>704</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B281" t="s">
-        <v>578</v>
+        <v>705</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>579</v>
+        <v>706</v>
       </c>
       <c r="E281" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G281" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B282" t="s">
-        <v>580</v>
+        <v>707</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>581</v>
+        <v>708</v>
       </c>
       <c r="E282" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G282" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B283" t="s">
-        <v>183</v>
+        <v>241</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="E283" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G283" s="16" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B284" t="s">
-        <v>582</v>
+        <v>709</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>583</v>
+        <v>710</v>
       </c>
       <c r="E284" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G284" s="16" t="s">
-        <v>584</v>
+        <v>711</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B285" t="s">
-        <v>585</v>
+        <v>712</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>586</v>
+        <v>713</v>
       </c>
       <c r="E285" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G285" s="16" t="s">
-        <v>587</v>
+        <v>714</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B286" t="s">
-        <v>588</v>
+        <v>715</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>589</v>
+        <v>716</v>
       </c>
       <c r="E286" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G286" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B287" t="s">
-        <v>590</v>
+        <v>717</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>591</v>
+        <v>718</v>
       </c>
       <c r="E287" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G287" s="16" t="s">
-        <v>592</v>
+        <v>719</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B288" t="s">
-        <v>593</v>
+        <v>720</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>594</v>
+        <v>721</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G288" s="16" t="s">
-        <v>595</v>
+        <v>722</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B289" t="s">
-        <v>596</v>
+        <v>723</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>597</v>
+        <v>724</v>
       </c>
       <c r="E289" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G289" s="16" t="s">
-        <v>598</v>
+        <v>725</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B290" t="s">
-        <v>599</v>
+        <v>726</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>600</v>
+        <v>727</v>
       </c>
       <c r="E290" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G290" s="16" t="s">
-        <v>601</v>
+        <v>728</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B291" t="s">
-        <v>602</v>
+        <v>729</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E291" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G291" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B292" t="s">
-        <v>603</v>
+        <v>730</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E292" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G292" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B293" t="s">
-        <v>604</v>
+        <v>731</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>605</v>
+        <v>732</v>
       </c>
       <c r="E293" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G293" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7026,7 +8785,7 @@
     </row>
     <row r="295" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>606</v>
+        <v>733</v>
       </c>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -7036,376 +8795,376 @@
     </row>
     <row r="296" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B296" t="s">
-        <v>607</v>
+        <v>734</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>608</v>
+        <v>735</v>
       </c>
       <c r="E296" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G296" s="16" t="s">
-        <v>609</v>
+        <v>736</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B297" t="s">
-        <v>610</v>
+        <v>737</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>611</v>
+        <v>738</v>
       </c>
       <c r="E297" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G297" s="16" t="s">
-        <v>612</v>
+        <v>739</v>
       </c>
     </row>
     <row r="298" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B298" t="s">
-        <v>613</v>
+        <v>740</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>614</v>
+        <v>741</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G298" s="16" t="s">
-        <v>615</v>
+        <v>742</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B299" t="s">
-        <v>616</v>
+        <v>743</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>617</v>
+        <v>744</v>
       </c>
       <c r="E299" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G299" s="16" t="s">
-        <v>618</v>
+        <v>745</v>
       </c>
     </row>
     <row r="300" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B300" t="s">
-        <v>619</v>
+        <v>746</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>620</v>
+        <v>747</v>
       </c>
       <c r="E300" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G300" s="16" t="s">
-        <v>621</v>
+        <v>748</v>
       </c>
     </row>
     <row r="301" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B301" t="s">
-        <v>622</v>
+        <v>749</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>623</v>
+        <v>750</v>
       </c>
       <c r="E301" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G301" s="16" t="s">
-        <v>624</v>
+        <v>751</v>
       </c>
     </row>
     <row r="302" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B302" t="s">
-        <v>625</v>
+        <v>752</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>626</v>
+        <v>753</v>
       </c>
       <c r="E302" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G302" s="16" t="s">
-        <v>627</v>
+        <v>754</v>
       </c>
     </row>
     <row r="303" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B303" t="s">
-        <v>628</v>
+        <v>755</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>629</v>
+        <v>756</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G303" s="16" t="s">
-        <v>630</v>
+        <v>757</v>
       </c>
     </row>
     <row r="304" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B304" t="s">
-        <v>631</v>
+        <v>758</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>632</v>
+        <v>759</v>
       </c>
       <c r="E304" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G304" s="16" t="s">
-        <v>633</v>
+        <v>760</v>
       </c>
     </row>
     <row r="305" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B305" t="s">
-        <v>634</v>
+        <v>761</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>635</v>
+        <v>762</v>
       </c>
       <c r="E305" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G305" s="16" t="s">
-        <v>636</v>
+        <v>763</v>
       </c>
     </row>
     <row r="306" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B306" t="s">
-        <v>637</v>
+        <v>764</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>638</v>
+        <v>765</v>
       </c>
       <c r="E306" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G306" s="16" t="s">
-        <v>639</v>
+        <v>766</v>
       </c>
     </row>
     <row r="307" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B307" t="s">
-        <v>640</v>
+        <v>767</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>641</v>
+        <v>768</v>
       </c>
       <c r="E307" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G307" s="16" t="s">
-        <v>642</v>
+        <v>769</v>
       </c>
     </row>
     <row r="308" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B308" t="s">
-        <v>643</v>
+        <v>770</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>644</v>
+        <v>771</v>
       </c>
       <c r="E308" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G308" s="16" t="s">
-        <v>645</v>
+        <v>772</v>
       </c>
     </row>
     <row r="309" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B309" t="s">
-        <v>646</v>
+        <v>773</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>644</v>
+        <v>771</v>
       </c>
       <c r="E309" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G309" s="16" t="s">
-        <v>647</v>
+        <v>774</v>
       </c>
     </row>
     <row r="310" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B310" t="s">
-        <v>648</v>
+        <v>775</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>649</v>
+        <v>776</v>
       </c>
       <c r="E310" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G310" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="311" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B311" t="s">
-        <v>650</v>
+        <v>777</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>651</v>
+        <v>778</v>
       </c>
       <c r="E311" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G311" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="312" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B312" t="s">
-        <v>652</v>
+        <v>779</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>653</v>
+        <v>780</v>
       </c>
       <c r="E312" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G312" s="16" t="s">
-        <v>654</v>
+        <v>781</v>
       </c>
     </row>
     <row r="313" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B313" t="s">
-        <v>655</v>
+        <v>782</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>656</v>
+        <v>783</v>
       </c>
       <c r="E313" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G313" s="16" t="s">
-        <v>657</v>
+        <v>784</v>
       </c>
     </row>
     <row r="314" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B314" t="s">
-        <v>658</v>
+        <v>785</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E314" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G314" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="315" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B315" t="s">
-        <v>659</v>
+        <v>786</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E315" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G315" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="316" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B316" t="s">
-        <v>660</v>
+        <v>787</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="E316" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G316" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="317" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B317" t="s">
-        <v>661</v>
+        <v>788</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>662</v>
+        <v>789</v>
       </c>
       <c r="E317" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="G317" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318" spans="2:7" x14ac:dyDescent="0.2">
@@ -7514,77 +9273,84 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="7" max="7" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>663</v>
+        <v>790</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>664</v>
+        <v>791</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>791</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>665</v>
+        <v>793</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>794</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>667</v>
+        <v>796</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>669</v>
+        <v>798</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>671</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/CodeDo_Editor_capacity_with_visual_explanations.xlsx
+++ b/CodeDo_Editor_capacity_with_visual_explanations.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/PersonalProjects/CodeDoRN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE95A5F-1F81-344D-90AF-E3EBBB2EE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D68BD-123D-2A40-83DE-6C7228A4A195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeDo Curriculum" sheetId="1" r:id="rId1"/>
     <sheet name="Legend" sheetId="2" r:id="rId2"/>
+    <sheet name="Visual Explanations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="804">
   <si>
     <t>World</t>
   </si>
@@ -3149,12 +3150,21 @@
   <si>
     <t>No meaningful way to execute this in a JS-based simulator (real JVM/threads/tooling/compiler-only features). Best taught via Learn/Explore/MCQ, not Write &amp; Run or Debug.</t>
   </si>
+  <si>
+    <t>Visual Explanation Lessons</t>
+  </si>
+  <si>
+    <t>192 lessons marked for a visual explanation in CodeDo Curriculum.</t>
+  </si>
+  <si>
+    <t>Recommended visual explanation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3215,8 +3225,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3248,8 +3292,13 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3264,11 +3313,128 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF2F5597"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF2F5597"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2F5597"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF2F5597"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2F5597"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF2F5597"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF2F5597"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF2F5597"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3316,6 +3482,48 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3559,7 +3767,7 @@
     <col min="4" max="4" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="4.33203125" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="7" max="7" width="51.6640625" customWidth="1"/>
     <col min="8" max="8" width="100" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9283,7 +9491,7 @@
     <col min="7" max="7" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>790</v>
       </c>
@@ -9300,7 +9508,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
@@ -9317,7 +9525,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
@@ -9331,7 +9539,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>242</v>
       </c>
@@ -9345,7 +9553,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>338</v>
       </c>
@@ -9356,4 +9564,2163 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF4472C4"/>
+  </sheetPr>
+  <dimension ref="A2:C197"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
+        <v>801</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="35" t="s">
+        <v>802</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+    </row>
+    <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C73" s="28" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="C89" s="28" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" s="28" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="C103" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B104" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C109" s="28" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B110" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B112" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="C112" s="28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B114" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="C115" s="28" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="C116" s="28" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="C117" s="28" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="C118" s="28" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="C119" s="28" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="C120" s="28" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="C121" s="28" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="C122" s="28" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="C123" s="28" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="C125" s="28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="C126" s="28" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" s="28" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="C128" s="28" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="C130" s="28" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="C131" s="28" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="C132" s="28" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B133" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="C133" s="28" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B134" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="C134" s="28" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="C135" s="28" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="B136" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B137" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="C137" s="28" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="C138" s="28" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>567</v>
+      </c>
+      <c r="C139" s="28" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B140" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="C140" s="28" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>575</v>
+      </c>
+      <c r="C141" s="28" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B142" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="C142" s="28" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B143" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="C143" s="28" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B144" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="C144" s="28" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B145" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="C145" s="28" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="C146" s="28" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>596</v>
+      </c>
+      <c r="C147" s="28" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B148" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="C148" s="28" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B149" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="C149" s="28" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B150" s="27" t="s">
+        <v>605</v>
+      </c>
+      <c r="C150" s="28" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B151" s="27" t="s">
+        <v>608</v>
+      </c>
+      <c r="C151" s="28" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B152" s="27" t="s">
+        <v>611</v>
+      </c>
+      <c r="C152" s="28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>614</v>
+      </c>
+      <c r="C153" s="28" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B154" s="27" t="s">
+        <v>617</v>
+      </c>
+      <c r="C154" s="28" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>620</v>
+      </c>
+      <c r="C155" s="28" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="B156" s="27" t="s">
+        <v>624</v>
+      </c>
+      <c r="C156" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>629</v>
+      </c>
+      <c r="C157" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B158" s="27" t="s">
+        <v>632</v>
+      </c>
+      <c r="C158" s="28" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>635</v>
+      </c>
+      <c r="C159" s="28" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>638</v>
+      </c>
+      <c r="C160" s="28" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B161" s="27" t="s">
+        <v>641</v>
+      </c>
+      <c r="C161" s="28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B162" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="C162" s="28" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="C163" s="28" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B164" s="27" t="s">
+        <v>658</v>
+      </c>
+      <c r="C164" s="28" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>670</v>
+      </c>
+      <c r="C165" s="28" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B166" s="27" t="s">
+        <v>673</v>
+      </c>
+      <c r="C166" s="28" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>676</v>
+      </c>
+      <c r="C167" s="28" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B168" s="27" t="s">
+        <v>679</v>
+      </c>
+      <c r="C168" s="28" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B169" s="27" t="s">
+        <v>682</v>
+      </c>
+      <c r="C169" s="28" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B170" s="27" t="s">
+        <v>685</v>
+      </c>
+      <c r="C170" s="28" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="C171" s="28" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="B172" s="27" t="s">
+        <v>693</v>
+      </c>
+      <c r="C172" s="28" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B173" s="27" t="s">
+        <v>699</v>
+      </c>
+      <c r="C173" s="28" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>702</v>
+      </c>
+      <c r="C174" s="28" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B175" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C175" s="28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B176" s="27" t="s">
+        <v>709</v>
+      </c>
+      <c r="C176" s="28" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>712</v>
+      </c>
+      <c r="C177" s="28" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>717</v>
+      </c>
+      <c r="C178" s="28" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B179" s="27" t="s">
+        <v>720</v>
+      </c>
+      <c r="C179" s="28" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B180" s="27" t="s">
+        <v>723</v>
+      </c>
+      <c r="C180" s="28" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B181" s="27" t="s">
+        <v>726</v>
+      </c>
+      <c r="C181" s="28" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>734</v>
+      </c>
+      <c r="C182" s="28" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>737</v>
+      </c>
+      <c r="C183" s="28" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>740</v>
+      </c>
+      <c r="C184" s="28" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B185" s="27" t="s">
+        <v>743</v>
+      </c>
+      <c r="C185" s="28" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B186" s="27" t="s">
+        <v>746</v>
+      </c>
+      <c r="C186" s="28" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B187" s="27" t="s">
+        <v>749</v>
+      </c>
+      <c r="C187" s="28" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B188" s="27" t="s">
+        <v>752</v>
+      </c>
+      <c r="C188" s="28" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>755</v>
+      </c>
+      <c r="C189" s="28" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B190" s="27" t="s">
+        <v>758</v>
+      </c>
+      <c r="C190" s="28" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B191" s="27" t="s">
+        <v>761</v>
+      </c>
+      <c r="C191" s="28" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B192" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="C192" s="28" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B193" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C193" s="28" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B194" s="27" t="s">
+        <v>770</v>
+      </c>
+      <c r="C194" s="28" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>773</v>
+      </c>
+      <c r="C195" s="28" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="B196" s="27" t="s">
+        <v>779</v>
+      </c>
+      <c r="C196" s="28" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="33" t="s">
+        <v>733</v>
+      </c>
+      <c r="B197" s="29" t="s">
+        <v>782</v>
+      </c>
+      <c r="C197" s="30" t="s">
+        <v>784</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>